--- a/BackEnd/Server/Controllers/FastReport/TaxTemplates/Mau_Phieu_thu.xlsx
+++ b/BackEnd/Server/Controllers/FastReport/TaxTemplates/Mau_Phieu_thu.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BUSINESS DEVELOPMENT\PHAM MEM SAO BAC DAU\UP PM THUE\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377FB690-3374-4EDB-AD0B-333D215BAB22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="19320" windowHeight="12220"/>
   </bookViews>
   <sheets>
     <sheet name="CT" sheetId="1" r:id="rId1"/>
@@ -34,21 +28,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Ma_vv</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Tiền VND</t>
   </si>
   <si>
     <t>TK Tiền mặt</t>
-  </si>
-  <si>
-    <t>1111</t>
   </si>
   <si>
     <t>Tk đối ứnng</t>
@@ -60,13 +48,7 @@
     <t>Ma_dvcs</t>
   </si>
   <si>
-    <t>CONGTY</t>
-  </si>
-  <si>
     <t>Ma_nt</t>
-  </si>
-  <si>
-    <t>VND</t>
   </si>
   <si>
     <t>Tiền nt</t>
@@ -89,74 +71,11 @@
   <si>
     <t>Tû gi¸</t>
   </si>
-  <si>
-    <t>PT001</t>
-  </si>
-  <si>
-    <t>PT002</t>
-  </si>
-  <si>
-    <t>PT003</t>
-  </si>
-  <si>
-    <t>PT004</t>
-  </si>
-  <si>
-    <t>TrÇn v¨n A</t>
-  </si>
-  <si>
-    <t>NguyÔn B</t>
-  </si>
-  <si>
-    <t>¤ng bµ g× ®ã</t>
-  </si>
-  <si>
-    <t>NguyÔn thÞ C</t>
-  </si>
-  <si>
-    <t>Thu tiÒn b¸n hµng</t>
-  </si>
-  <si>
-    <t>Thu l¹i tiÒn t¹m øng</t>
-  </si>
-  <si>
-    <t>TiÒn hµng</t>
-  </si>
-  <si>
-    <t>TiÒn thuÕ GTGT</t>
-  </si>
-  <si>
-    <t>13111</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>51111</t>
-  </si>
-  <si>
-    <t>33311</t>
-  </si>
-  <si>
-    <t>Thu c«ng nî</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1001 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1002 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1003 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">K.H1004 </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
@@ -248,9 +167,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -288,7 +207,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -360,7 +279,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -533,1809 +452,1658 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N527"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="7"/>
-    <col min="4" max="4" width="19.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="10" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="14.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" style="7"/>
+    <col min="4" max="4" width="19.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="29.54296875" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" style="10" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
-        <v>45654</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="10">
-        <v>4500000</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>45655</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="10">
-        <v>1500000</v>
-      </c>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="J3" s="4"/>
-      <c r="M3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
-        <v>45656</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="10">
-        <v>700000</v>
-      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
       <c r="J4" s="4"/>
-      <c r="M4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>45657</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="10">
-        <v>950000</v>
-      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="C5" s="8"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
       <c r="J5" s="4"/>
-      <c r="M5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
-        <v>45657</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="10">
-        <v>870000</v>
-      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="C6" s="8"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
       <c r="J6" s="4"/>
-      <c r="M6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="6"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="6"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="6"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="6"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="6"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="6"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="6"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="6"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="6"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="6"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="6"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="6"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="6"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
     </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
     </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
     </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
     </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
     </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
     </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
     </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
     </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
     </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
     </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
     </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
     </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
     </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
     </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
     </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
     </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
     </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
     </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
     </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
     </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
     </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
     </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
     </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
     </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
     </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
     </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
     </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
     </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
     </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
     </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
     </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
     </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
     </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
     </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
     </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
     </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
     </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
     </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
     </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
     </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
     </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
     </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A501" s="6"/>
     </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A502" s="6"/>
     </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A503" s="6"/>
     </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A504" s="6"/>
     </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A505" s="6"/>
     </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A506" s="6"/>
     </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A507" s="6"/>
     </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A508" s="6"/>
     </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A509" s="6"/>
     </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A510" s="6"/>
     </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A511" s="6"/>
     </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A512" s="6"/>
     </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A513" s="6"/>
     </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A514" s="6"/>
     </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A515" s="6"/>
     </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A516" s="6"/>
     </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A517" s="6"/>
     </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A518" s="6"/>
     </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A519" s="6"/>
     </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A520" s="6"/>
     </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A521" s="6"/>
     </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A522" s="6"/>
     </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A523" s="6"/>
     </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A524" s="6"/>
     </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A525" s="6"/>
     </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A526" s="6"/>
     </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A527" s="6"/>
     </row>
   </sheetData>
